--- a/output/monthly_abb_report.xlsx
+++ b/output/monthly_abb_report.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Monthly ABB Details" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly ABB Details" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -88,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -98,12 +98,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -471,11 +465,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="53" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
@@ -487,7 +481,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Monthly ABB Statement - Account No: 10000950117</t>
+          <t>Monthly ABB Statement - Account No: 57500001116530</t>
         </is>
       </c>
     </row>
@@ -537,365 +531,29 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Jul-2024</t>
+          <t>Feb-2026</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>857014.58</v>
+        <v>109381798.75</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>857014.58</v>
+        <v>245234541.98</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>857014.58</v>
+        <v>78495518.55</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>857014.58</v>
+        <v>23214556.27</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>125752.58</v>
+        <v>110404590.76</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>265520.58</v>
+        <v>297355687.11</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>636555.2466666667</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Aug-2024</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>439278.84</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>339279.84</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>418388.84</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>256388.84</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>878221.84</v>
-      </c>
-      <c r="G5" s="6" t="n">
-        <v>679421.84</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>501830.0066666667</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Sep-2024</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>769955.84</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>3203.84</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>682951.34</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>509952.34</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>693083.77</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>553203.77</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>535391.8166666667</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Oct-2024</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>295974.78</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>521315.78</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>517718.68</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>432026.68</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>431130.68</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>377677.68</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>429307.3800000001</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Nov-2024</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>377577.68</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>175341.68</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>1201688.02</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>108170.99</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>108170.99</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>342139.99</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>385514.8916666667</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Dec-2024</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>2326139.99</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>326171.03</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>720167.03</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>568592.99</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>568610.9300000001</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>536649.9300000001</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>841055.3166666668</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Jan-2025</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>536918.9399999999</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>1286908.94</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>278907.94</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>662810.5600000001</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>449810.56</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>447700.56</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>610509.5833333334</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Feb-2025</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>547700.5600000001</v>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>1497700.56</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>114928.74</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>550558.74</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>550558.74</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>46749.74</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>551366.1800000001</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Mar-2025</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>46749.74</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>368106.04</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>362006.04</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>389106.04</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>262160.74</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>258316.74</v>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>281074.2233333333</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Apr-2025</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n">
-        <v>277560.53</v>
-      </c>
-      <c r="C13" s="6" t="n">
-        <v>277560.53</v>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>269250.53</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>117652.53</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>232652.53</v>
-      </c>
-      <c r="G13" s="6" t="n">
-        <v>228691.53</v>
-      </c>
-      <c r="H13" s="6" t="n">
-        <v>233894.6966666667</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>May-2025</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>228691.53</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>228691.53</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>400691.53</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>245159.35</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>593016.35</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>281916.35</v>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>329694.44</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Jun-2025</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n">
-        <v>51916.35</v>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>134916.35</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>126447.35</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>84447.35000000001</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>133447.35</v>
-      </c>
-      <c r="G15" s="6" t="n">
-        <v>230386.35</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>126926.85</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Jul-2025</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>200594.03</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>237224.03</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>1146899.23</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>3828019.23</v>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>1852937.23</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>1852937.23</v>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>1519768.496666667</v>
+        <v>144014448.9033333</v>
       </c>
     </row>
   </sheetData>
